--- a/orders.xlsx
+++ b/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="1122">
   <si>
     <t>313</t>
   </si>
@@ -3373,16 +3373,10 @@
     <t>+380660254324</t>
   </si>
   <si>
-    <t>Stefan Merfort</t>
-  </si>
-  <si>
     <t>+380937606718</t>
   </si>
   <si>
     <t>Ярослав Васюта</t>
-  </si>
-  <si>
-    <t>+436602470704</t>
   </si>
   <si>
     <t>Васюта Ольга</t>
@@ -3815,10 +3809,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1122</v>
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -3847,7 +3841,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1118</v>
@@ -3879,10 +3873,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1122</v>
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -3911,10 +3905,10 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1122</v>
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>20</v>
@@ -4039,10 +4033,10 @@
         <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>46</v>
@@ -4071,7 +4065,7 @@
         <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>1118</v>
@@ -4103,10 +4097,10 @@
         <v>52</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>53</v>
@@ -4135,10 +4129,10 @@
         <v>57</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>60</v>
@@ -4231,7 +4225,7 @@
         <v>72</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>1118</v>

--- a/orders.xlsx
+++ b/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="1124">
   <si>
     <t>313</t>
   </si>
@@ -3380,6 +3380,12 @@
   </si>
   <si>
     <t>Васюта Ольга</t>
+  </si>
+  <si>
+    <t>Никита Мемес</t>
+  </si>
+  <si>
+    <t>+380993360403</t>
   </si>
 </sst>
 </file>
@@ -3809,10 +3815,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>1122</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1123</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -3873,10 +3879,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>1122</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1123</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -3905,10 +3911,10 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>1122</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1123</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>20</v>
